--- a/artfynd/A 32046-2026 artfynd.xlsx
+++ b/artfynd/A 32046-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136218260</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32046-2026 artfynd.xlsx
+++ b/artfynd/A 32046-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136218260</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32046-2026 artfynd.xlsx
+++ b/artfynd/A 32046-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136218260</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32046-2026 artfynd.xlsx
+++ b/artfynd/A 32046-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136218260</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
